--- a/mock-data/out/장비 목록_유선_20260828.xlsx
+++ b/mock-data/out/장비 목록_유선_20260828.xlsx
@@ -524,7 +524,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASSET0001</t>
+          <t>ASSET0007</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -534,17 +534,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KT-SW-BUSAN-01</t>
+          <t>KTDB070</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.10.3.144</t>
+          <t>10.21.2.184</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -584,12 +584,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -599,14 +599,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUSAN IDC Switch</t>
+          <t>SEOUL IDC L4</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>46262</v>
+        <v>46252</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="T2" s="1" t="n">
-        <v>45599</v>
+        <v>45393</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASSET0002</t>
+          <t>ASSET0048</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KT-RT-INCHEON-02</t>
+          <t>KTDB002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.10.10.169</t>
+          <t>10.21.1.6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>INCHEON IDC Router</t>
+          <t>INCHEON IDC Switch</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="T3" s="1" t="n">
-        <v>46131</v>
+        <v>45452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASSET0003</t>
+          <t>ASSET0062</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KT-RT-BUSAN-03</t>
+          <t>KTCLD043</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10.10.2.49</t>
+          <t>10.20.2.52</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -786,19 +786,19 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUSAN IDC Router</t>
+          <t>GWANGJU IDC Firewall</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R4" s="1" t="n">
-        <v>46261</v>
+        <v>46257</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="T4" s="1" t="n">
-        <v>45368</v>
+        <v>46186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASSET0004</t>
+          <t>ASSET0035</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -822,17 +822,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KT-VPN-DAEJEON-04</t>
+          <t>KTGE036</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.10.9.98</t>
+          <t>10.23.1.182</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -852,22 +852,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>IOS-XE</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -887,28 +887,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DAEJEON IDC VPN</t>
+          <t>DAEJEON IDC Router</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>46260</v>
+        <v>46252</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="T5" s="1" t="n">
-        <v>45940</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASSET0005</t>
+          <t>ASSET0031</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -918,17 +918,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KT-SW-DAEJEON-05</t>
+          <t>KTIPTV042</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.10.19.169</t>
+          <t>10.22.1.244</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cloud사업팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PAN-OS</t>
+          <t>IOS-XE</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>46261</v>
+        <v>46241</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="T6" s="1" t="n">
-        <v>45419</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASSET0006</t>
+          <t>ASSET0058</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KT-VPN-SEOUL-06</t>
+          <t>KTDB045</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.10.18.105</t>
+          <t>10.21.2.46</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1074,19 +1074,19 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>SEOUL IDC VPN</t>
+          <t>GWANGJU IDC Router</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="T7" s="1" t="n">
-        <v>45519</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASSET0007</t>
+          <t>ASSET0029</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KT-L4-SEOUL-07</t>
+          <t>KTBCP001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10.10.4.45</t>
+          <t>10.25.1.2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SEOUL IDC L4</t>
+          <t>INCHEON IDC VPN</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="T8" s="1" t="n">
-        <v>45393</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASSET0008</t>
+          <t>ASSET0005</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KT-RT-BUSAN-08</t>
+          <t>KTDB071</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.10.11.243</t>
+          <t>10.21.2.195</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>Cloud사업팀</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>IOS-XE</t>
+          <t>PAN-OS</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1271,14 +1271,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BUSAN IDC Router</t>
+          <t>DAEJEON IDC Switch</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="T9" s="1" t="n">
-        <v>45438</v>
+        <v>45419</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASSET0009</t>
+          <t>ASSET0061</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KT-L4-INCHEON-09</t>
+          <t>KTCLD037</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.10.9.14</t>
+          <t>10.20.1.243</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1332,42 +1332,42 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cloud사업팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>PAN-OS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>INCHEON IDC L4</t>
+          <t>SEOUL IDC L4</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1382,13 +1382,13 @@
         </is>
       </c>
       <c r="T10" s="1" t="n">
-        <v>45730</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASSET0010</t>
+          <t>ASSET0057</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1398,17 +1398,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KT-VPN-BUSAN-10</t>
+          <t>KTAI010</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.10.10.163</t>
+          <t>10.24.1.58</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>JunOS</t>
+          <t>IOS-XE</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1463,28 +1463,28 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>BUSAN IDC VPN</t>
+          <t>DAEJEON IDC L4</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="T11" s="1" t="n">
-        <v>45796</v>
+        <v>45674</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASSET0011</t>
+          <t>ASSET0027</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1494,17 +1494,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KT-RT-GWANGJU-11</t>
+          <t>KTAI003</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10.10.17.239</t>
+          <t>10.24.1.25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1514,32 +1514,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>Cloud사업팀</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>JunOS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>GWANGJU IDC Router</t>
+          <t>GWANGJU IDC Switch</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="T12" s="1" t="n">
-        <v>45727</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASSET0012</t>
+          <t>ASSET0046</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KT-VPN-DAEJEON-12</t>
+          <t>KTAI068</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10.10.8.190</t>
+          <t>10.24.2.167</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1610,32 +1610,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>PAN-OS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DAEJEON IDC VPN</t>
+          <t>DAEJEON IDC L4</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="T13" s="1" t="n">
-        <v>45344</v>
+        <v>45874</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASSET0013</t>
+          <t>ASSET0011</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KT-L4-GWANGJU-13</t>
+          <t>KTBCP004</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10.10.13.44</t>
+          <t>10.25.1.10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>JunOS</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1741,24 +1741,24 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>GWANGJU IDC L4</t>
+          <t>GWANGJU IDC Router</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>46261</v>
+        <v>46252</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="T14" s="1" t="n">
-        <v>46047</v>
+        <v>45727</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASSET0014</t>
+          <t>ASSET0042</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1782,17 +1782,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KT-VPN-GWANGJU-14</t>
+          <t>KTCLD018</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10.10.7.237</t>
+          <t>10.20.1.150</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>Cloud사업팀</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>46227</v>
+        <v>46242</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="T15" s="1" t="n">
-        <v>45298</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASSET0015</t>
+          <t>ASSET0066</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KT-VPN-GWANGJU-15</t>
+          <t>KTCLD061</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.10.11.77</t>
+          <t>10.20.2.175</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>GWANGJU IDC VPN</t>
+          <t>GWANGJU IDC Switch</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -1954,17 +1954,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="T16" s="1" t="n">
-        <v>45449</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASSET0016</t>
+          <t>ASSET0047</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KT-L4-SEOUL-16</t>
+          <t>KTBCP054</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.10.16.2</t>
+          <t>10.25.2.16</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2004,22 +2004,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>PAN-OS</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>SEOUL IDC L4</t>
+          <t>BUSAN IDC L4</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="T17" s="1" t="n">
-        <v>45403</v>
+        <v>46061</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASSET0017</t>
+          <t>ASSET0024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2070,17 +2070,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KT-L4-GWANGJU-17</t>
+          <t>KTCLD040</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10.10.6.36</t>
+          <t>10.20.2.5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2100,22 +2100,22 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>JunOS</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2130,19 +2130,19 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>GWANGJU IDC L4</t>
+          <t>GWANGJU IDC Firewall</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>46260</v>
+        <v>46236</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2150,13 +2150,13 @@
         </is>
       </c>
       <c r="T18" s="1" t="n">
-        <v>45324</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASSET0018</t>
+          <t>ASSET0041</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KT-SW-BUSAN-18</t>
+          <t>KTDB059</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10.10.16.246</t>
+          <t>10.21.2.134</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>JunOS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2231,14 +2231,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUSAN IDC Switch</t>
+          <t>DAEJEON IDC Firewall</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>46257</v>
+        <v>46243</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2246,13 +2246,13 @@
         </is>
       </c>
       <c r="T19" s="1" t="n">
-        <v>46051</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASSET0019</t>
+          <t>ASSET0069</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2262,17 +2262,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KT-L4-BUSAN-19</t>
+          <t>KTIPTV013</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.10.4.246</t>
+          <t>10.22.1.77</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2292,22 +2292,22 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>IOS-XE</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2322,33 +2322,33 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUSAN IDC L4</t>
+          <t>INCHEON IDC Firewall</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>46261</v>
+        <v>46257</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="T20" s="1" t="n">
-        <v>46047</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASSET0020</t>
+          <t>ASSET0022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KT-RT-GWANGJU-20</t>
+          <t>KTGE071</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10.10.16.75</t>
+          <t>10.23.2.144</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>GWANGJU IDC Router</t>
+          <t>GWANGJU IDC Switch</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="T21" s="1" t="n">
-        <v>45545</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASSET0021</t>
+          <t>ASSET0026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KT-L4-BUSAN-21</t>
+          <t>KTAI009</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10.10.16.181</t>
+          <t>10.24.1.50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2484,27 +2484,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>Cloud사업팀</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>IOS-XE</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2514,19 +2514,19 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUSAN IDC L4</t>
+          <t>BUSAN IDC Switch</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>46261</v>
+        <v>46228</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2534,13 +2534,13 @@
         </is>
       </c>
       <c r="T22" s="1" t="n">
-        <v>45488</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASSET0022</t>
+          <t>ASSET0012</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2550,17 +2550,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KT-SW-GWANGJU-22</t>
+          <t>KTIPTV029</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10.10.1.158</t>
+          <t>10.22.1.157</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>PAN-OS</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>GWANGJU IDC Switch</t>
+          <t>DAEJEON IDC VPN</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -2630,13 +2630,13 @@
         </is>
       </c>
       <c r="T23" s="1" t="n">
-        <v>45951</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASSET0023</t>
+          <t>ASSET0049</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KT-RT-DAEJEON-23</t>
+          <t>KTGE042</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10.10.4.69</t>
+          <t>10.23.1.233</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2681,22 +2681,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>IOS-XE</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2706,19 +2706,19 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DAEJEON IDC Router</t>
+          <t>SEOUL IDC Firewall</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>46225</v>
+        <v>46262</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="T24" s="1" t="n">
-        <v>45509</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASSET0024</t>
+          <t>ASSET0013</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KT-FW-GWANGJU-24</t>
+          <t>KTCLD024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10.10.9.233</t>
+          <t>10.20.1.181</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>JunOS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2802,19 +2802,19 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>GWANGJU IDC Firewall</t>
+          <t>GWANGJU IDC L4</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>46236</v>
+        <v>46261</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="T25" s="1" t="n">
-        <v>46051</v>
+        <v>46047</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ASSET0025</t>
+          <t>ASSET0018</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KT-FW-INCHEON-25</t>
+          <t>KTGE030</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.10.17.155</t>
+          <t>10.23.1.133</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2868,22 +2868,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>JunOS</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2898,19 +2898,19 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>INCHEON IDC Firewall</t>
+          <t>BUSAN IDC Switch</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>46261</v>
+        <v>46257</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="T26" s="1" t="n">
-        <v>46197</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ASSET0026</t>
+          <t>ASSET0010</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KT-SW-BUSAN-26</t>
+          <t>KTIPTV043</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10.10.15.237</t>
+          <t>10.22.1.251</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2964,27 +2964,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cloud사업팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>JunOS</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2999,14 +2999,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUSAN IDC Switch</t>
+          <t>BUSAN IDC VPN</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>46228</v>
+        <v>46262</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3014,13 +3014,13 @@
         </is>
       </c>
       <c r="T27" s="1" t="n">
-        <v>45422</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ASSET0027</t>
+          <t>ASSET0033</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3030,17 +3030,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KT-SW-GWANGJU-27</t>
+          <t>KTBCP037</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10.10.18.183</t>
+          <t>10.25.1.188</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3050,32 +3050,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Cloud사업팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>PAN-OS</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3095,14 +3095,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>GWANGJU IDC Switch</t>
+          <t>SEOUL IDC VPN</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="T28" s="1" t="n">
-        <v>45721</v>
+        <v>45529</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ASSET0028</t>
+          <t>ASSET0050</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KT-VPN-INCHEON-28</t>
+          <t>KTCLD002</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10.10.1.43</t>
+          <t>10.20.1.8</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3186,19 +3186,19 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>INCHEON IDC VPN</t>
+          <t>BUSAN IDC L4</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3206,13 +3206,13 @@
         </is>
       </c>
       <c r="T29" s="1" t="n">
-        <v>45798</v>
+        <v>45458</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ASSET0029</t>
+          <t>ASSET0065</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3222,17 +3222,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KT-VPN-INCHEON-29</t>
+          <t>KTDB067</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10.10.3.43</t>
+          <t>10.21.2.171</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>Cloud사업팀</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3282,33 +3282,33 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>INCHEON IDC VPN</t>
+          <t>SEOUL IDC Firewall</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="T30" s="1" t="n">
-        <v>46005</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ASSET0030</t>
+          <t>ASSET0017</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KT-RT-INCHEON-30</t>
+          <t>KTBCP094</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10.10.15.129</t>
+          <t>10.25.2.244</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3348,22 +3348,22 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>PAN-OS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>INCHEON IDC Router</t>
+          <t>GWANGJU IDC L4</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -3398,13 +3398,13 @@
         </is>
       </c>
       <c r="T31" s="1" t="n">
-        <v>45946</v>
+        <v>45324</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ASSET0031</t>
+          <t>ASSET0055</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KT-SW-DAEJEON-31</t>
+          <t>KTCLD019</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10.10.5.70</t>
+          <t>10.20.1.156</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3444,22 +3444,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>Cloud사업팀</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>IOS-XE</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3479,14 +3479,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DAEJEON IDC Switch</t>
+          <t>SEOUL IDC L4</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>46241</v>
+        <v>46262</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="T32" s="1" t="n">
-        <v>46014</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ASSET0032</t>
+          <t>ASSET0052</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KT-VPN-DAEJEON-32</t>
+          <t>KTCLD051</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10.10.5.105</t>
+          <t>10.20.2.111</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3530,32 +3530,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>JunOS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3565,38 +3565,38 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DAEJEON IDC VPN</t>
+          <t>SEOUL IDC L4</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="T33" s="1" t="n">
-        <v>46180</v>
+        <v>46011</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ASSET0033</t>
+          <t>ASSET0028</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3606,17 +3606,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KT-VPN-SEOUL-33</t>
+          <t>KTDB076</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10.10.13.243</t>
+          <t>10.21.2.222</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3636,22 +3636,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>PAN-OS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3666,19 +3666,19 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>SEOUL IDC VPN</t>
+          <t>INCHEON IDC VPN</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3686,13 +3686,13 @@
         </is>
       </c>
       <c r="T34" s="1" t="n">
-        <v>45529</v>
+        <v>45798</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ASSET0034</t>
+          <t>ASSET0032</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3702,17 +3702,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KT-L4-DAEJEON-34</t>
+          <t>KTIPTV076</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10.10.5.231</t>
+          <t>10.22.2.190</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3732,22 +3732,22 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>JunOS</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3767,14 +3767,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DAEJEON IDC L4</t>
+          <t>DAEJEON IDC VPN</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>46257</v>
+        <v>46262</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3782,13 +3782,13 @@
         </is>
       </c>
       <c r="T35" s="1" t="n">
-        <v>45580</v>
+        <v>46180</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ASSET0035</t>
+          <t>ASSET0004</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3798,17 +3798,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KT-RT-DAEJEON-35</t>
+          <t>KTCLD062</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10.10.6.227</t>
+          <t>10.20.2.179</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3828,22 +3828,22 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>IOS-XE</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3863,28 +3863,28 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>DAEJEON IDC Router</t>
+          <t>DAEJEON IDC VPN</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="T36" s="1" t="n">
-        <v>45394</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ASSET0036</t>
+          <t>ASSET0008</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KT-VPN-BUSAN-36</t>
+          <t>KTIPTV054</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10.10.1.155</t>
+          <t>10.22.2.53</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3924,22 +3924,22 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>IOS-XE</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3954,19 +3954,19 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUSAN IDC VPN</t>
+          <t>BUSAN IDC Router</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>46262</v>
+        <v>46257</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="T37" s="1" t="n">
-        <v>45934</v>
+        <v>45438</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ASSET0037</t>
+          <t>ASSET0053</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3990,17 +3990,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KT-VPN-SEOUL-37</t>
+          <t>KTCLD007</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10.10.1.246</t>
+          <t>10.20.1.59</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Cloud사업팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4030,17 +4030,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>PAN-OS</t>
+          <t>IOS-XE</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4055,14 +4055,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>SEOUL IDC VPN</t>
+          <t>DAEJEON IDC Router</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>46262</v>
+        <v>46257</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4070,13 +4070,13 @@
         </is>
       </c>
       <c r="T38" s="1" t="n">
-        <v>45349</v>
+        <v>45932</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ASSET0038</t>
+          <t>ASSET0014</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4086,17 +4086,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KT-VPN-DAEJEON-38</t>
+          <t>KTAI057</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>10.10.18.32</t>
+          <t>10.24.2.99</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Cloud사업팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4146,19 +4146,19 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>DAEJEON IDC VPN</t>
+          <t>GWANGJU IDC VPN</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>46252</v>
+        <v>46227</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4166,13 +4166,13 @@
         </is>
       </c>
       <c r="T39" s="1" t="n">
-        <v>45686</v>
+        <v>45298</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ASSET0039</t>
+          <t>ASSET0003</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KT-SW-DAEJEON-39</t>
+          <t>KTIPTV078</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10.10.10.58</t>
+          <t>10.22.2.198</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>PAN-OS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4242,19 +4242,19 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>DAEJEON IDC Switch</t>
+          <t>BUSAN IDC Router</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         </is>
       </c>
       <c r="T40" s="1" t="n">
-        <v>45378</v>
+        <v>45368</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ASSET0040</t>
+          <t>ASSET0030</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KT-RT-INCHEON-40</t>
+          <t>KTCLD053</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.10.5.46</t>
+          <t>10.20.2.120</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4308,22 +4308,22 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>PAN-OS</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4358,13 +4358,13 @@
         </is>
       </c>
       <c r="T41" s="1" t="n">
-        <v>45803</v>
+        <v>45946</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ASSET0041</t>
+          <t>ASSET0001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4374,17 +4374,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KT-FW-DAEJEON-41</t>
+          <t>KTAI052</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.10.3.202</t>
+          <t>10.24.2.75</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4434,19 +4434,19 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>DAEJEON IDC Firewall</t>
+          <t>BUSAN IDC Switch</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>46243</v>
+        <v>46262</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4454,13 +4454,13 @@
         </is>
       </c>
       <c r="T42" s="1" t="n">
-        <v>45407</v>
+        <v>45599</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASSET0042</t>
+          <t>ASSET0070</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KT-VPN-GWANGJU-42</t>
+          <t>KTIPTV001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.10.9.38</t>
+          <t>10.22.1.12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4490,17 +4490,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Cloud사업팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4535,28 +4535,28 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>GWANGJU IDC VPN</t>
+          <t>BUSAN IDC L4</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>46242</v>
+        <v>46261</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="T43" s="1" t="n">
-        <v>45943</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ASSET0043</t>
+          <t>ASSET0009</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4566,17 +4566,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KT-FW-BUSAN-43</t>
+          <t>KTAI077</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10.10.8.99</t>
+          <t>10.24.2.223</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4596,27 +4596,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>Cloud사업팀</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>PAN-OS</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4626,19 +4626,19 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>BUSAN IDC Firewall</t>
+          <t>INCHEON IDC L4</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4646,13 +4646,13 @@
         </is>
       </c>
       <c r="T44" s="1" t="n">
-        <v>46087</v>
+        <v>45730</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ASSET0044</t>
+          <t>ASSET0063</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4667,12 +4667,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KT-SW-SEOUL-44</t>
+          <t>KTIPTV020</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>10.10.8.93</t>
+          <t>10.22.1.114</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4682,37 +4682,37 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>JunOS</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4727,14 +4727,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>SEOUL IDC Switch</t>
+          <t>GWANGJU IDC L4</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>46247</v>
+        <v>46257</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4742,13 +4742,13 @@
         </is>
       </c>
       <c r="T45" s="1" t="n">
-        <v>46161</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ASSET0045</t>
+          <t>ASSET0039</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KT-SW-DAEJEON-45</t>
+          <t>KTIPTV058</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>10.10.15.37</t>
+          <t>10.22.2.85</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4838,13 +4838,13 @@
         </is>
       </c>
       <c r="T46" s="1" t="n">
-        <v>46004</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ASSET0046</t>
+          <t>ASSET0021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KT-L4-DAEJEON-46</t>
+          <t>KTGE015</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>10.10.2.180</t>
+          <t>10.23.1.74</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4879,27 +4879,27 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>IOS-XE</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4919,14 +4919,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>DAEJEON IDC L4</t>
+          <t>BUSAN IDC L4</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4934,13 +4934,13 @@
         </is>
       </c>
       <c r="T47" s="1" t="n">
-        <v>45874</v>
+        <v>45488</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ASSET0047</t>
+          <t>ASSET0038</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KT-L4-BUSAN-47</t>
+          <t>KTBCP036</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10.10.6.121</t>
+          <t>10.25.1.184</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>Cloud사업팀</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>PAN-OS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5005,24 +5005,24 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>BUSAN IDC L4</t>
+          <t>DAEJEON IDC VPN</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>46260</v>
+        <v>46252</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="T48" s="1" t="n">
-        <v>46061</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ASSET0048</t>
+          <t>ASSET0020</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5046,17 +5046,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KT-SW-INCHEON-48</t>
+          <t>KTAI002</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10.10.6.3</t>
+          <t>10.24.1.17</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>INCHEON IDC Switch</t>
+          <t>GWANGJU IDC Router</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -5122,17 +5122,17 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="T49" s="1" t="n">
-        <v>45452</v>
+        <v>45545</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ASSET0049</t>
+          <t>ASSET0060</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5142,17 +5142,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KT-FW-SEOUL-49</t>
+          <t>KTGE029</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10.10.17.97</t>
+          <t>10.23.1.127</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5172,27 +5172,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>IOS-XE</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5202,19 +5202,19 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>SEOUL IDC Firewall</t>
+          <t>SEOUL IDC Router</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>46262</v>
+        <v>46235</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5222,13 +5222,13 @@
         </is>
       </c>
       <c r="T50" s="1" t="n">
-        <v>45706</v>
+        <v>46011</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ASSET0050</t>
+          <t>ASSET0019</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5238,17 +5238,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KT-L4-BUSAN-50</t>
+          <t>KTDB042</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>10.10.2.206</t>
+          <t>10.21.2.43</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5307,24 +5307,24 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="T51" s="1" t="n">
-        <v>45458</v>
+        <v>46047</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ASSET0051</t>
+          <t>ASSET0064</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KT-VPN-SEOUL-51</t>
+          <t>KTAI063</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>10.10.3.55</t>
+          <t>10.24.2.127</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5364,22 +5364,22 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>JunOS</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5399,14 +5399,14 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>SEOUL IDC VPN</t>
+          <t>GWANGJU IDC Switch</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>46260</v>
+        <v>46252</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5414,13 +5414,13 @@
         </is>
       </c>
       <c r="T52" s="1" t="n">
-        <v>45869</v>
+        <v>46046</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ASSET0052</t>
+          <t>ASSET0002</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5430,17 +5430,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KT-L4-SEOUL-52</t>
+          <t>KTGE066</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>10.10.2.81</t>
+          <t>10.23.2.104</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5450,17 +5450,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5490,33 +5490,33 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>SEOUL IDC L4</t>
+          <t>INCHEON IDC Router</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="T53" s="1" t="n">
-        <v>46011</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ASSET0053</t>
+          <t>ASSET0015</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KT-RT-DAEJEON-53</t>
+          <t>KTIPTV039</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>10.10.14.230</t>
+          <t>10.22.1.222</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5561,17 +5561,17 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>IOS-XE</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5586,19 +5586,19 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>DAEJEON IDC Router</t>
+          <t>GWANGJU IDC VPN</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5606,13 +5606,13 @@
         </is>
       </c>
       <c r="T54" s="1" t="n">
-        <v>45932</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ASSET0054</t>
+          <t>ASSET0037</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5622,17 +5622,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KT-RT-BUSAN-54</t>
+          <t>KTIPTV034</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>10.10.7.207</t>
+          <t>10.22.1.186</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5642,17 +5642,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>Cloud사업팀</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5662,17 +5662,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>IOS-XE</t>
+          <t>PAN-OS</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5687,14 +5687,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>BUSAN IDC Router</t>
+          <t>SEOUL IDC VPN</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>46231</v>
+        <v>46262</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5702,13 +5702,13 @@
         </is>
       </c>
       <c r="T55" s="1" t="n">
-        <v>46168</v>
+        <v>45349</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ASSET0055</t>
+          <t>ASSET0059</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5718,17 +5718,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KT-L4-SEOUL-55</t>
+          <t>KTGE011</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>10.10.13.62</t>
+          <t>10.23.1.77</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cloud사업팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5778,27 +5778,27 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>SEOUL IDC L4</t>
+          <t>DAEJEON IDC Router</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="T56" s="1" t="n">
-        <v>46108</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="57">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KT-RT-GWANGJU-56</t>
+          <t>KTCLD011</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10.10.4.117</t>
+          <t>10.20.1.146</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5900,7 +5900,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ASSET0057</t>
+          <t>ASSET0016</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KT-L4-DAEJEON-57</t>
+          <t>KTDB024</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>10.10.15.167</t>
+          <t>10.21.1.238</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>IOS-XE</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5975,28 +5975,28 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>DAEJEON IDC L4</t>
+          <t>SEOUL IDC L4</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="T58" s="1" t="n">
-        <v>45674</v>
+        <v>45403</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ASSET0058</t>
+          <t>ASSET0044</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6006,17 +6006,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KT-RT-GWANGJU-58</t>
+          <t>KTBCP013</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10.10.17.116</t>
+          <t>10.25.1.119</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6026,17 +6026,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>NW운용1팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6066,19 +6066,19 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>GWANGJU IDC Router</t>
+          <t>SEOUL IDC Switch</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>46262</v>
+        <v>46247</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="T59" s="1" t="n">
-        <v>46165</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASSET0059</t>
+          <t>ASSET0067</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6102,17 +6102,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KT-RT-DAEJEON-59</t>
+          <t>KTC-LD015</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10.10.13.41</t>
+          <t>10.20.1.142</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6162,33 +6162,33 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>DAEJEON IDC Router</t>
+          <t>SEOUL IDC VPN</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="T60" s="1" t="n">
-        <v>45768</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ASSET0060</t>
+          <t>ASSET0006</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KT-RT-SEOUL-60</t>
+          <t>KTIP-TV060</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>10.10.6.188</t>
+          <t>10.22.2.95</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6258,19 +6258,19 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>SEOUL IDC Router</t>
+          <t>SEOUL IDC VPN</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>46235</v>
+        <v>46260</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6278,13 +6278,13 @@
         </is>
       </c>
       <c r="T61" s="1" t="n">
-        <v>46011</v>
+        <v>45519</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ASSET0061</t>
+          <t>ASSET0025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KT-L4-SEOUL-61</t>
+          <t>KT-GE053</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10.10.9.117</t>
+          <t>10.23.2.26</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6349,24 +6349,24 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>SEOUL IDC L4</t>
+          <t>INCHEON IDC Firewall</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6374,13 +6374,13 @@
         </is>
       </c>
       <c r="T62" s="1" t="n">
-        <v>46119</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ASSET0062</t>
+          <t>ASSET0040</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6390,17 +6390,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KT-FW-GWANGJU-62</t>
+          <t>KTIP-TV041</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10.10.16.55</t>
+          <t>10.22.1.232</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6450,19 +6450,19 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-01</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>GWANGJU IDC Firewall</t>
+          <t>INCHEON IDC Router</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="T63" s="1" t="n">
-        <v>46186</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASSET0063</t>
+          <t>ASSET0036</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KT-L4-GWANGJU-63</t>
+          <t>KT-VPN-BUSAN-36</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>10.10.17.55</t>
+          <t>10.10.1.155</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6506,32 +6506,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>JunOS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6551,14 +6551,14 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>GWANGJU IDC L4</t>
+          <t>BUSAN IDC VPN</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>46257</v>
+        <v>46262</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6566,13 +6566,13 @@
         </is>
       </c>
       <c r="T64" s="1" t="n">
-        <v>45840</v>
+        <v>45934</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASSET0064</t>
+          <t>ASSET0054</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6582,17 +6582,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>인프라부문</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KT-SW-GWANGJU-64</t>
+          <t>KT-RT-BUSAN-54</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>10.10.12.234</t>
+          <t>10.10.7.207</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6602,17 +6602,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>운영</t>
+          <t>개발</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>NW운용2팀</t>
+          <t>IDC운용팀</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>JunOS</t>
+          <t>IOS-XE</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6637,24 +6637,24 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>NTP-GROUP-03</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>GWANGJU IDC Switch</t>
+          <t>BUSAN IDC Router</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46252</v>
+        <v>46231</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6662,13 +6662,13 @@
         </is>
       </c>
       <c r="T65" s="1" t="n">
-        <v>46046</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ASSET0065</t>
+          <t>ASSET0051</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KT-FW-SEOUL-65</t>
+          <t>KT-VPN-SEOUL-51</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10.10.5.230</t>
+          <t>10.10.3.55</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Cloud사업팀</t>
+          <t>NW운용1팀</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>SEOUL IDC Firewall</t>
+          <t>SEOUL IDC VPN</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -6754,17 +6754,17 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="T66" s="1" t="n">
-        <v>46169</v>
+        <v>45869</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ASSET0066</t>
+          <t>ASSET0043</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KT-SW-GWANGJU-66</t>
+          <t>KT-FW-BUSAN-43</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>10.10.19.25</t>
+          <t>10.10.8.99</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6834,33 +6834,33 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-02</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>GWANGJU IDC Switch</t>
+          <t>BUSAN IDC Firewall</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>46261</v>
+        <v>46252</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="T67" s="1" t="n">
-        <v>45987</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ASSET0067</t>
+          <t>ASSET0045</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6870,17 +6870,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>인프라부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KT-VPN-SEOUL-67</t>
+          <t>KT-SW-DAEJEON-45</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>10.10.12.209</t>
+          <t>10.10.15.37</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6905,22 +6905,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>PAN-OS</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>적용</t>
+          <t>미적용</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6935,14 +6935,14 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>SEOUL IDC VPN</t>
+          <t>DAEJEON IDC Switch</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R68" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6950,13 +6950,13 @@
         </is>
       </c>
       <c r="T68" s="1" t="n">
-        <v>45652</v>
+        <v>46004</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ASSET0068</t>
+          <t>ASSET0034</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KT-FW-INCHEON-68</t>
+          <t>KT-L4-DAEJEON-34</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>10.10.14.134</t>
+          <t>10.10.5.231</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7001,17 +7001,17 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>JunOS</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7031,14 +7031,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>INCHEON IDC Firewall</t>
+          <t>DAEJEON IDC L4</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R69" s="1" t="n">
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7046,13 +7046,13 @@
         </is>
       </c>
       <c r="T69" s="1" t="n">
-        <v>45739</v>
+        <v>45580</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ASSET0069</t>
+          <t>ASSET0023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7062,17 +7062,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>네트워크부문</t>
+          <t>보안부문</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KT-FW-INCHEON-69</t>
+          <t>KT-RT-DAEJEON-23</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>10.10.4.23</t>
+          <t>10.10.4.69</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Firewall</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Network OS</t>
+          <t>Linux</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>IOS-XE</t>
+          <t>Rocky Linux</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7122,19 +7122,19 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>NTP-GROUP-01</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>INCHEON IDC Firewall</t>
+          <t>DAEJEON IDC Router</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="R70" s="1" t="n">
-        <v>46257</v>
+        <v>46225</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="T70" s="1" t="n">
-        <v>46164</v>
+        <v>45509</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ASSET0070</t>
+          <t>ASSET0068</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7158,17 +7158,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>보안부문</t>
+          <t>네트워크부문</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KT-L4-BUSAN-70</t>
+          <t>KT-FW-INCHEON-68</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10.10.8.199</t>
+          <t>10.10.14.134</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7178,67 +7178,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>Firewall</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>개발</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>IDC운용팀</t>
+          <t>NW운용2팀</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Linux</t>
+          <t>Network OS</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Rocky Linux</t>
+          <t>JunOS</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>미적용</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>NTP-GROUP-02</t>
+          <t>NTP-GROUP-03</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>BUSAN IDC L4</t>
+          <t>INCHEON IDC Firewall</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R71" s="1" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="T71" s="1" t="n">
-        <v>45952</v>
+        <v>45739</v>
       </c>
     </row>
   </sheetData>
